--- a/AAII_Financials/Yearly/SGAMY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SGAMY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -712,16 +712,16 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2587200</v>
+        <v>2626100</v>
       </c>
       <c r="E8" s="3">
-        <v>2131100</v>
+        <v>2163200</v>
       </c>
       <c r="F8" s="3">
-        <v>1844200</v>
+        <v>1872000</v>
       </c>
       <c r="G8" s="3">
-        <v>2434200</v>
+        <v>2470800</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
@@ -742,16 +742,16 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1537600</v>
+        <v>1560800</v>
       </c>
       <c r="E9" s="3">
-        <v>1282100</v>
+        <v>1301400</v>
       </c>
       <c r="F9" s="3">
-        <v>1175100</v>
+        <v>1192800</v>
       </c>
       <c r="G9" s="3">
-        <v>1527800</v>
+        <v>1550800</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -772,16 +772,16 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1049600</v>
+        <v>1065400</v>
       </c>
       <c r="E10" s="3">
-        <v>849000</v>
+        <v>861800</v>
       </c>
       <c r="F10" s="3">
-        <v>669100</v>
+        <v>679200</v>
       </c>
       <c r="G10" s="3">
-        <v>906400</v>
+        <v>920000</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -816,16 +816,16 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>153000</v>
+        <v>155300</v>
       </c>
       <c r="E12" s="3">
-        <v>139000</v>
+        <v>141100</v>
       </c>
       <c r="F12" s="3">
-        <v>150000</v>
+        <v>152300</v>
       </c>
       <c r="G12" s="3">
-        <v>164100</v>
+        <v>166600</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
@@ -876,16 +876,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>17900</v>
+        <v>18200</v>
       </c>
       <c r="E14" s="3">
-        <v>6900</v>
+        <v>7000</v>
       </c>
       <c r="F14" s="3">
-        <v>254800</v>
+        <v>258700</v>
       </c>
       <c r="G14" s="3">
-        <v>8200</v>
+        <v>8300</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -947,16 +947,16 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2294400</v>
+        <v>2328900</v>
       </c>
       <c r="E17" s="3">
-        <v>1925300</v>
+        <v>1954300</v>
       </c>
       <c r="F17" s="3">
-        <v>2055600</v>
+        <v>2086500</v>
       </c>
       <c r="G17" s="3">
-        <v>2258800</v>
+        <v>2292800</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
@@ -977,16 +977,16 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>292800</v>
+        <v>297200</v>
       </c>
       <c r="E18" s="3">
-        <v>205800</v>
+        <v>208900</v>
       </c>
       <c r="F18" s="3">
-        <v>-211300</v>
+        <v>-214500</v>
       </c>
       <c r="G18" s="3">
-        <v>175400</v>
+        <v>178000</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -1021,16 +1021,16 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>21900</v>
+        <v>22200</v>
       </c>
       <c r="E20" s="3">
-        <v>48000</v>
+        <v>48700</v>
       </c>
       <c r="F20" s="3">
-        <v>149100</v>
+        <v>151300</v>
       </c>
       <c r="G20" s="3">
-        <v>7800</v>
+        <v>7900</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1051,16 +1051,16 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>399600</v>
+        <v>406400</v>
       </c>
       <c r="E21" s="3">
-        <v>344500</v>
+        <v>350500</v>
       </c>
       <c r="F21" s="3">
-        <v>48400</v>
+        <v>50100</v>
       </c>
       <c r="G21" s="3">
-        <v>310300</v>
+        <v>316100</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
@@ -1081,13 +1081,13 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="E22" s="3">
         <v>2000</v>
       </c>
       <c r="F22" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="G22" s="3">
         <v>3200</v>
@@ -1111,16 +1111,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>312500</v>
+        <v>317200</v>
       </c>
       <c r="E23" s="3">
-        <v>251800</v>
+        <v>255600</v>
       </c>
       <c r="F23" s="3">
-        <v>-65400</v>
+        <v>-66300</v>
       </c>
       <c r="G23" s="3">
-        <v>180000</v>
+        <v>182700</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
@@ -1141,16 +1141,16 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>7500</v>
+        <v>7700</v>
       </c>
       <c r="E24" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="F24" s="3">
-        <v>-77800</v>
+        <v>-79000</v>
       </c>
       <c r="G24" s="3">
-        <v>87200</v>
+        <v>88500</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1201,16 +1201,16 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>305000</v>
+        <v>309600</v>
       </c>
       <c r="E26" s="3">
-        <v>245800</v>
+        <v>249500</v>
       </c>
       <c r="F26" s="3">
-        <v>12500</v>
+        <v>12700</v>
       </c>
       <c r="G26" s="3">
-        <v>92800</v>
+        <v>94200</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
@@ -1231,16 +1231,16 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>305000</v>
+        <v>309600</v>
       </c>
       <c r="E27" s="3">
-        <v>245900</v>
+        <v>249600</v>
       </c>
       <c r="F27" s="3">
-        <v>8500</v>
+        <v>8600</v>
       </c>
       <c r="G27" s="3">
-        <v>91500</v>
+        <v>92800</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
@@ -1381,16 +1381,16 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-21900</v>
+        <v>-22200</v>
       </c>
       <c r="E32" s="3">
-        <v>-48000</v>
+        <v>-48700</v>
       </c>
       <c r="F32" s="3">
-        <v>-149100</v>
+        <v>-151300</v>
       </c>
       <c r="G32" s="3">
-        <v>-7800</v>
+        <v>-7900</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1411,16 +1411,16 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>305000</v>
+        <v>309600</v>
       </c>
       <c r="E33" s="3">
-        <v>245900</v>
+        <v>249600</v>
       </c>
       <c r="F33" s="3">
-        <v>8500</v>
+        <v>8600</v>
       </c>
       <c r="G33" s="3">
-        <v>91500</v>
+        <v>92800</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
@@ -1471,16 +1471,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>305000</v>
+        <v>309600</v>
       </c>
       <c r="E35" s="3">
-        <v>245900</v>
+        <v>249600</v>
       </c>
       <c r="F35" s="3">
-        <v>8500</v>
+        <v>8600</v>
       </c>
       <c r="G35" s="3">
-        <v>91500</v>
+        <v>92800</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
@@ -1564,16 +1564,16 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1191900</v>
+        <v>1209900</v>
       </c>
       <c r="E41" s="3">
-        <v>1012300</v>
+        <v>1027600</v>
       </c>
       <c r="F41" s="3">
-        <v>1029000</v>
+        <v>1044500</v>
       </c>
       <c r="G41" s="3">
-        <v>1055800</v>
+        <v>1071700</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
@@ -1600,10 +1600,10 @@
         <v>3</v>
       </c>
       <c r="F42" s="3">
-        <v>4800</v>
+        <v>4900</v>
       </c>
       <c r="G42" s="3">
-        <v>35800</v>
+        <v>36400</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
@@ -1624,16 +1624,16 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>456100</v>
+        <v>462900</v>
       </c>
       <c r="E43" s="3">
-        <v>334900</v>
+        <v>340000</v>
       </c>
       <c r="F43" s="3">
-        <v>320300</v>
+        <v>325200</v>
       </c>
       <c r="G43" s="3">
-        <v>298400</v>
+        <v>302900</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -1654,16 +1654,16 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>594000</v>
+        <v>603000</v>
       </c>
       <c r="E44" s="3">
-        <v>448400</v>
+        <v>455100</v>
       </c>
       <c r="F44" s="3">
-        <v>351300</v>
+        <v>356600</v>
       </c>
       <c r="G44" s="3">
-        <v>312100</v>
+        <v>316800</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -1684,16 +1684,16 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>107600</v>
+        <v>109200</v>
       </c>
       <c r="E45" s="3">
-        <v>115300</v>
+        <v>117000</v>
       </c>
       <c r="F45" s="3">
-        <v>129100</v>
+        <v>131100</v>
       </c>
       <c r="G45" s="3">
-        <v>83800</v>
+        <v>85000</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -1714,16 +1714,16 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2349600</v>
+        <v>2385000</v>
       </c>
       <c r="E46" s="3">
-        <v>1910900</v>
+        <v>1939700</v>
       </c>
       <c r="F46" s="3">
-        <v>1834600</v>
+        <v>1862200</v>
       </c>
       <c r="G46" s="3">
-        <v>1786000</v>
+        <v>1812900</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
@@ -1744,16 +1744,16 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>261600</v>
+        <v>265600</v>
       </c>
       <c r="E47" s="3">
-        <v>270500</v>
+        <v>274600</v>
       </c>
       <c r="F47" s="3">
-        <v>254300</v>
+        <v>258100</v>
       </c>
       <c r="G47" s="3">
-        <v>369900</v>
+        <v>375500</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -1774,16 +1774,16 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>401600</v>
+        <v>407600</v>
       </c>
       <c r="E48" s="3">
-        <v>400800</v>
+        <v>406800</v>
       </c>
       <c r="F48" s="3">
-        <v>409100</v>
+        <v>415300</v>
       </c>
       <c r="G48" s="3">
-        <v>575300</v>
+        <v>584000</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -1804,16 +1804,16 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>88000</v>
+        <v>89300</v>
       </c>
       <c r="E49" s="3">
-        <v>87500</v>
+        <v>88900</v>
       </c>
       <c r="F49" s="3">
-        <v>99600</v>
+        <v>101100</v>
       </c>
       <c r="G49" s="3">
-        <v>119300</v>
+        <v>121100</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
@@ -1894,16 +1894,16 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>229600</v>
+        <v>233000</v>
       </c>
       <c r="E52" s="3">
-        <v>221900</v>
+        <v>225300</v>
       </c>
       <c r="F52" s="3">
-        <v>201800</v>
+        <v>204900</v>
       </c>
       <c r="G52" s="3">
-        <v>192300</v>
+        <v>195200</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -1954,16 +1954,16 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3330400</v>
+        <v>3380600</v>
       </c>
       <c r="E54" s="3">
-        <v>2891700</v>
+        <v>2935200</v>
       </c>
       <c r="F54" s="3">
-        <v>2799400</v>
+        <v>2841600</v>
       </c>
       <c r="G54" s="3">
-        <v>3042900</v>
+        <v>3088700</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
@@ -2012,16 +2012,16 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>202900</v>
+        <v>205900</v>
       </c>
       <c r="E57" s="3">
-        <v>162400</v>
+        <v>164800</v>
       </c>
       <c r="F57" s="3">
-        <v>112800</v>
+        <v>114500</v>
       </c>
       <c r="G57" s="3">
-        <v>118400</v>
+        <v>120200</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
@@ -2042,16 +2042,16 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>122200</v>
+        <v>124100</v>
       </c>
       <c r="E58" s="3">
-        <v>74100</v>
+        <v>75200</v>
       </c>
       <c r="F58" s="3">
-        <v>7700</v>
+        <v>7800</v>
       </c>
       <c r="G58" s="3">
-        <v>161000</v>
+        <v>163500</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
@@ -2072,16 +2072,16 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>473900</v>
+        <v>481000</v>
       </c>
       <c r="E59" s="3">
-        <v>341100</v>
+        <v>346300</v>
       </c>
       <c r="F59" s="3">
-        <v>276400</v>
+        <v>280500</v>
       </c>
       <c r="G59" s="3">
-        <v>292600</v>
+        <v>297000</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -2102,16 +2102,16 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>799000</v>
+        <v>811000</v>
       </c>
       <c r="E60" s="3">
-        <v>577600</v>
+        <v>586300</v>
       </c>
       <c r="F60" s="3">
-        <v>396900</v>
+        <v>402900</v>
       </c>
       <c r="G60" s="3">
-        <v>572000</v>
+        <v>580600</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
@@ -2132,16 +2132,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>268700</v>
+        <v>272800</v>
       </c>
       <c r="E61" s="3">
-        <v>306300</v>
+        <v>310900</v>
       </c>
       <c r="F61" s="3">
-        <v>378000</v>
+        <v>383700</v>
       </c>
       <c r="G61" s="3">
-        <v>369100</v>
+        <v>374600</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2162,16 +2162,16 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>62500</v>
+        <v>63500</v>
       </c>
       <c r="E62" s="3">
-        <v>64700</v>
+        <v>65600</v>
       </c>
       <c r="F62" s="3">
-        <v>90600</v>
+        <v>91900</v>
       </c>
       <c r="G62" s="3">
-        <v>130700</v>
+        <v>132600</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2282,16 +2282,16 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1130400</v>
+        <v>1147400</v>
       </c>
       <c r="E66" s="3">
-        <v>948900</v>
+        <v>963200</v>
       </c>
       <c r="F66" s="3">
-        <v>868800</v>
+        <v>881900</v>
       </c>
       <c r="G66" s="3">
-        <v>1084700</v>
+        <v>1101000</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
@@ -2446,16 +2446,16 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1741700</v>
+        <v>1768000</v>
       </c>
       <c r="E72" s="3">
-        <v>1493100</v>
+        <v>1515600</v>
       </c>
       <c r="F72" s="3">
-        <v>1331700</v>
+        <v>1351700</v>
       </c>
       <c r="G72" s="3">
-        <v>1375500</v>
+        <v>1396200</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -2566,16 +2566,16 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2200000</v>
+        <v>2233100</v>
       </c>
       <c r="E76" s="3">
-        <v>1942800</v>
+        <v>1972000</v>
       </c>
       <c r="F76" s="3">
-        <v>1930600</v>
+        <v>1959700</v>
       </c>
       <c r="G76" s="3">
-        <v>1958200</v>
+        <v>1987700</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
@@ -2661,16 +2661,16 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>305000</v>
+        <v>309600</v>
       </c>
       <c r="E81" s="3">
-        <v>245900</v>
+        <v>249600</v>
       </c>
       <c r="F81" s="3">
-        <v>8500</v>
+        <v>8600</v>
       </c>
       <c r="G81" s="3">
-        <v>91500</v>
+        <v>92800</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
@@ -2705,16 +2705,16 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>85300</v>
+        <v>86600</v>
       </c>
       <c r="E83" s="3">
-        <v>91100</v>
+        <v>92500</v>
       </c>
       <c r="F83" s="3">
-        <v>111100</v>
+        <v>112800</v>
       </c>
       <c r="G83" s="3">
-        <v>127700</v>
+        <v>129700</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -2885,16 +2885,16 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>296100</v>
+        <v>300600</v>
       </c>
       <c r="E89" s="3">
-        <v>263300</v>
+        <v>267300</v>
       </c>
       <c r="F89" s="3">
-        <v>-42300</v>
+        <v>-42900</v>
       </c>
       <c r="G89" s="3">
-        <v>256000</v>
+        <v>259800</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
@@ -2929,16 +2929,16 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-32800</v>
+        <v>-33300</v>
       </c>
       <c r="E91" s="3">
-        <v>-39700</v>
+        <v>-40300</v>
       </c>
       <c r="F91" s="3">
-        <v>-48800</v>
+        <v>-49500</v>
       </c>
       <c r="G91" s="3">
-        <v>-66600</v>
+        <v>-67600</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
@@ -3019,16 +3019,16 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-15600</v>
+        <v>-15800</v>
       </c>
       <c r="E94" s="3">
-        <v>-58400</v>
+        <v>-59300</v>
       </c>
       <c r="F94" s="3">
-        <v>202300</v>
+        <v>205400</v>
       </c>
       <c r="G94" s="3">
-        <v>-102700</v>
+        <v>-104200</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -3063,16 +3063,16 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-58900</v>
+        <v>-59800</v>
       </c>
       <c r="E96" s="3">
-        <v>-62500</v>
+        <v>-63400</v>
       </c>
       <c r="F96" s="3">
-        <v>-46900</v>
+        <v>-47600</v>
       </c>
       <c r="G96" s="3">
-        <v>-62400</v>
+        <v>-63300</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
@@ -3183,16 +3183,16 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-102000</v>
+        <v>-103500</v>
       </c>
       <c r="E100" s="3">
-        <v>-238800</v>
+        <v>-242400</v>
       </c>
       <c r="F100" s="3">
-        <v>-209100</v>
+        <v>-212300</v>
       </c>
       <c r="G100" s="3">
-        <v>-72700</v>
+        <v>-73800</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -3216,13 +3216,13 @@
         <v>1100</v>
       </c>
       <c r="E101" s="3">
-        <v>20100</v>
+        <v>20400</v>
       </c>
       <c r="F101" s="3">
-        <v>22000</v>
+        <v>22300</v>
       </c>
       <c r="G101" s="3">
-        <v>-10500</v>
+        <v>-10600</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
@@ -3243,16 +3243,16 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>179600</v>
+        <v>182300</v>
       </c>
       <c r="E102" s="3">
-        <v>-13800</v>
+        <v>-14000</v>
       </c>
       <c r="F102" s="3">
-        <v>-27100</v>
+        <v>-27500</v>
       </c>
       <c r="G102" s="3">
-        <v>70100</v>
+        <v>71100</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/SGAMY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SGAMY_YR_FIN.xlsx
@@ -656,46 +656,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44651</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44286</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43921</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I7" s="2" t="s">
         <v>3</v>
       </c>
@@ -705,26 +705,29 @@
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2626100</v>
+        <v>2985200</v>
       </c>
       <c r="E8" s="3">
-        <v>2163200</v>
+        <v>2485900</v>
       </c>
       <c r="F8" s="3">
-        <v>1872000</v>
+        <v>2047700</v>
       </c>
       <c r="G8" s="3">
-        <v>2470800</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
+        <v>1772000</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2338900</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
@@ -735,26 +738,29 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1560800</v>
+        <v>1730000</v>
       </c>
       <c r="E9" s="3">
-        <v>1301400</v>
+        <v>1477400</v>
       </c>
       <c r="F9" s="3">
-        <v>1192800</v>
+        <v>1231900</v>
       </c>
       <c r="G9" s="3">
-        <v>1550800</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
+        <v>1129100</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1468000</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
@@ -765,26 +771,29 @@
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1065400</v>
+        <v>1255200</v>
       </c>
       <c r="E10" s="3">
-        <v>861800</v>
+        <v>1008500</v>
       </c>
       <c r="F10" s="3">
-        <v>679200</v>
+        <v>815800</v>
       </c>
       <c r="G10" s="3">
-        <v>920000</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
+        <v>642900</v>
+      </c>
+      <c r="H10" s="3">
+        <v>870900</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
@@ -795,9 +804,12 @@
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,25 +822,26 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>155300</v>
+        <v>158600</v>
       </c>
       <c r="E12" s="3">
-        <v>141100</v>
+        <v>147000</v>
       </c>
       <c r="F12" s="3">
-        <v>152300</v>
+        <v>133600</v>
       </c>
       <c r="G12" s="3">
-        <v>166600</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
+        <v>144200</v>
+      </c>
+      <c r="H12" s="3">
+        <v>157700</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>3</v>
@@ -839,9 +852,12 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -869,26 +885,29 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>18200</v>
+        <v>118400</v>
       </c>
       <c r="E14" s="3">
-        <v>7000</v>
+        <v>17200</v>
       </c>
       <c r="F14" s="3">
-        <v>258700</v>
+        <v>6700</v>
       </c>
       <c r="G14" s="3">
-        <v>8300</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+        <v>244900</v>
+      </c>
+      <c r="H14" s="3">
+        <v>7900</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -899,9 +918,12 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -929,9 +951,12 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -941,25 +966,26 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2328900</v>
+        <v>2741000</v>
       </c>
       <c r="E17" s="3">
-        <v>1954300</v>
+        <v>2204500</v>
       </c>
       <c r="F17" s="3">
-        <v>2086500</v>
+        <v>1849900</v>
       </c>
       <c r="G17" s="3">
-        <v>2292800</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
+        <v>1975100</v>
+      </c>
+      <c r="H17" s="3">
+        <v>2170400</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>3</v>
@@ -970,26 +996,29 @@
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>297200</v>
+        <v>244200</v>
       </c>
       <c r="E18" s="3">
-        <v>208900</v>
+        <v>281300</v>
       </c>
       <c r="F18" s="3">
-        <v>-214500</v>
+        <v>197800</v>
       </c>
       <c r="G18" s="3">
-        <v>178000</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
+        <v>-203000</v>
+      </c>
+      <c r="H18" s="3">
+        <v>168500</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
@@ -1000,9 +1029,12 @@
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1015,25 +1047,26 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>22200</v>
+        <v>27600</v>
       </c>
       <c r="E20" s="3">
-        <v>48700</v>
+        <v>21000</v>
       </c>
       <c r="F20" s="3">
-        <v>151300</v>
+        <v>46100</v>
       </c>
       <c r="G20" s="3">
-        <v>7900</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
+        <v>143200</v>
+      </c>
+      <c r="H20" s="3">
+        <v>7500</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
@@ -1044,26 +1077,29 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>406400</v>
+        <v>373800</v>
       </c>
       <c r="E21" s="3">
-        <v>350500</v>
+        <v>384200</v>
       </c>
       <c r="F21" s="3">
-        <v>50100</v>
+        <v>331200</v>
       </c>
       <c r="G21" s="3">
-        <v>316100</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
+        <v>46800</v>
+      </c>
+      <c r="H21" s="3">
+        <v>298500</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
@@ -1074,26 +1110,29 @@
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2200</v>
+        <v>4900</v>
       </c>
       <c r="E22" s="3">
         <v>2000</v>
       </c>
       <c r="F22" s="3">
-        <v>3200</v>
+        <v>1900</v>
       </c>
       <c r="G22" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
+        <v>3000</v>
+      </c>
+      <c r="H22" s="3">
+        <v>3000</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
@@ -1104,26 +1143,29 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>317200</v>
+        <v>266900</v>
       </c>
       <c r="E23" s="3">
-        <v>255600</v>
+        <v>300300</v>
       </c>
       <c r="F23" s="3">
-        <v>-66300</v>
+        <v>241900</v>
       </c>
       <c r="G23" s="3">
-        <v>182700</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
+        <v>-62800</v>
+      </c>
+      <c r="H23" s="3">
+        <v>172900</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>3</v>
@@ -1134,26 +1176,29 @@
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>7700</v>
+        <v>55500</v>
       </c>
       <c r="E24" s="3">
-        <v>6100</v>
+        <v>7200</v>
       </c>
       <c r="F24" s="3">
-        <v>-79000</v>
+        <v>5800</v>
       </c>
       <c r="G24" s="3">
-        <v>88500</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
+        <v>-74800</v>
+      </c>
+      <c r="H24" s="3">
+        <v>83800</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
@@ -1164,9 +1209,12 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1194,26 +1242,29 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>309600</v>
+        <v>211400</v>
       </c>
       <c r="E26" s="3">
-        <v>249500</v>
+        <v>293100</v>
       </c>
       <c r="F26" s="3">
-        <v>12700</v>
+        <v>236200</v>
       </c>
       <c r="G26" s="3">
-        <v>94200</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
+        <v>12000</v>
+      </c>
+      <c r="H26" s="3">
+        <v>89100</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>3</v>
@@ -1224,26 +1275,29 @@
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>309600</v>
+        <v>210900</v>
       </c>
       <c r="E27" s="3">
-        <v>249600</v>
+        <v>293100</v>
       </c>
       <c r="F27" s="3">
-        <v>8600</v>
+        <v>236200</v>
       </c>
       <c r="G27" s="3">
-        <v>92800</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
+        <v>8100</v>
+      </c>
+      <c r="H27" s="3">
+        <v>87900</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>3</v>
@@ -1254,9 +1308,12 @@
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1284,9 +1341,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1314,9 +1374,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1344,9 +1407,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1374,26 +1440,29 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-22200</v>
+        <v>-27600</v>
       </c>
       <c r="E32" s="3">
-        <v>-48700</v>
+        <v>-21000</v>
       </c>
       <c r="F32" s="3">
-        <v>-151300</v>
+        <v>-46100</v>
       </c>
       <c r="G32" s="3">
-        <v>-7900</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
+        <v>-143200</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-7500</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
@@ -1404,26 +1473,29 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>309600</v>
+        <v>210900</v>
       </c>
       <c r="E33" s="3">
-        <v>249600</v>
+        <v>293100</v>
       </c>
       <c r="F33" s="3">
-        <v>8600</v>
+        <v>236200</v>
       </c>
       <c r="G33" s="3">
-        <v>92800</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
+        <v>8100</v>
+      </c>
+      <c r="H33" s="3">
+        <v>87900</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>3</v>
@@ -1434,9 +1506,12 @@
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1464,26 +1539,29 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>309600</v>
+        <v>210900</v>
       </c>
       <c r="E35" s="3">
-        <v>249600</v>
+        <v>293100</v>
       </c>
       <c r="F35" s="3">
-        <v>8600</v>
+        <v>236200</v>
       </c>
       <c r="G35" s="3">
-        <v>92800</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
+        <v>8100</v>
+      </c>
+      <c r="H35" s="3">
+        <v>87900</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>3</v>
@@ -1494,32 +1572,35 @@
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44651</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44286</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43921</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1529,9 +1610,12 @@
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1544,8 +1628,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1558,25 +1643,26 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1209900</v>
+        <v>1350700</v>
       </c>
       <c r="E41" s="3">
-        <v>1027600</v>
+        <v>1145300</v>
       </c>
       <c r="F41" s="3">
-        <v>1044500</v>
+        <v>972700</v>
       </c>
       <c r="G41" s="3">
-        <v>1071700</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
+        <v>988700</v>
+      </c>
+      <c r="H41" s="3">
+        <v>1014500</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
@@ -1587,26 +1673,29 @@
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>51600</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F42" s="3">
-        <v>4900</v>
+      <c r="F42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G42" s="3">
-        <v>36400</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
+        <v>4600</v>
+      </c>
+      <c r="H42" s="3">
+        <v>34400</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>3</v>
@@ -1617,26 +1706,29 @@
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>462900</v>
+        <v>473800</v>
       </c>
       <c r="E43" s="3">
-        <v>340000</v>
+        <v>438200</v>
       </c>
       <c r="F43" s="3">
-        <v>325200</v>
+        <v>321800</v>
       </c>
       <c r="G43" s="3">
-        <v>302900</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
+        <v>307800</v>
+      </c>
+      <c r="H43" s="3">
+        <v>286700</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
@@ -1647,26 +1739,29 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>603000</v>
+        <v>521600</v>
       </c>
       <c r="E44" s="3">
-        <v>455100</v>
+        <v>570800</v>
       </c>
       <c r="F44" s="3">
-        <v>356600</v>
+        <v>430800</v>
       </c>
       <c r="G44" s="3">
-        <v>316800</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
+        <v>337600</v>
+      </c>
+      <c r="H44" s="3">
+        <v>299900</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
@@ -1677,26 +1772,29 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>109200</v>
+        <v>122300</v>
       </c>
       <c r="E45" s="3">
-        <v>117000</v>
+        <v>103400</v>
       </c>
       <c r="F45" s="3">
-        <v>131100</v>
+        <v>110800</v>
       </c>
       <c r="G45" s="3">
-        <v>85000</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
+        <v>124100</v>
+      </c>
+      <c r="H45" s="3">
+        <v>80500</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -1707,26 +1805,29 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2385000</v>
+        <v>2520100</v>
       </c>
       <c r="E46" s="3">
-        <v>1939700</v>
+        <v>2257600</v>
       </c>
       <c r="F46" s="3">
-        <v>1862200</v>
+        <v>1836100</v>
       </c>
       <c r="G46" s="3">
-        <v>1812900</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
+        <v>1762800</v>
+      </c>
+      <c r="H46" s="3">
+        <v>1716100</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
@@ -1737,26 +1838,29 @@
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>265600</v>
+        <v>366900</v>
       </c>
       <c r="E47" s="3">
-        <v>274600</v>
+        <v>251400</v>
       </c>
       <c r="F47" s="3">
-        <v>258100</v>
+        <v>259900</v>
       </c>
       <c r="G47" s="3">
-        <v>375500</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
+        <v>244300</v>
+      </c>
+      <c r="H47" s="3">
+        <v>355400</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
@@ -1767,26 +1871,29 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>407600</v>
+        <v>383400</v>
       </c>
       <c r="E48" s="3">
-        <v>406800</v>
+        <v>385900</v>
       </c>
       <c r="F48" s="3">
-        <v>415300</v>
+        <v>385100</v>
       </c>
       <c r="G48" s="3">
-        <v>584000</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
+        <v>393100</v>
+      </c>
+      <c r="H48" s="3">
+        <v>552800</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
@@ -1797,26 +1904,29 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>89300</v>
+        <v>588800</v>
       </c>
       <c r="E49" s="3">
-        <v>88900</v>
+        <v>84500</v>
       </c>
       <c r="F49" s="3">
-        <v>101100</v>
+        <v>84100</v>
       </c>
       <c r="G49" s="3">
-        <v>121100</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
+        <v>95700</v>
+      </c>
+      <c r="H49" s="3">
+        <v>114600</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
@@ -1827,9 +1937,12 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1857,9 +1970,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1887,26 +2003,29 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>233000</v>
+        <v>313200</v>
       </c>
       <c r="E52" s="3">
-        <v>225300</v>
+        <v>220600</v>
       </c>
       <c r="F52" s="3">
-        <v>204900</v>
+        <v>213200</v>
       </c>
       <c r="G52" s="3">
-        <v>195200</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
+        <v>193900</v>
+      </c>
+      <c r="H52" s="3">
+        <v>184800</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -1917,9 +2036,12 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1947,26 +2069,29 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3380600</v>
+        <v>4172500</v>
       </c>
       <c r="E54" s="3">
-        <v>2935200</v>
+        <v>3200000</v>
       </c>
       <c r="F54" s="3">
-        <v>2841600</v>
+        <v>2778400</v>
       </c>
       <c r="G54" s="3">
-        <v>3088700</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
+        <v>2689800</v>
+      </c>
+      <c r="H54" s="3">
+        <v>2923700</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
@@ -1977,9 +2102,12 @@
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1992,8 +2120,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2006,25 +2135,26 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>205900</v>
+        <v>166400</v>
       </c>
       <c r="E57" s="3">
-        <v>164800</v>
+        <v>194900</v>
       </c>
       <c r="F57" s="3">
-        <v>114500</v>
+        <v>156000</v>
       </c>
       <c r="G57" s="3">
-        <v>120200</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
+        <v>108400</v>
+      </c>
+      <c r="H57" s="3">
+        <v>113800</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
@@ -2035,26 +2165,29 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>124100</v>
+        <v>143600</v>
       </c>
       <c r="E58" s="3">
-        <v>75200</v>
+        <v>117400</v>
       </c>
       <c r="F58" s="3">
-        <v>7800</v>
+        <v>71200</v>
       </c>
       <c r="G58" s="3">
-        <v>163500</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
+        <v>7400</v>
+      </c>
+      <c r="H58" s="3">
+        <v>154700</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
@@ -2065,26 +2198,29 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>481000</v>
+        <v>554400</v>
       </c>
       <c r="E59" s="3">
-        <v>346300</v>
+        <v>455300</v>
       </c>
       <c r="F59" s="3">
-        <v>280500</v>
+        <v>327800</v>
       </c>
       <c r="G59" s="3">
-        <v>297000</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
+        <v>265500</v>
+      </c>
+      <c r="H59" s="3">
+        <v>281100</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
@@ -2095,26 +2231,29 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>811000</v>
+        <v>864500</v>
       </c>
       <c r="E60" s="3">
-        <v>586300</v>
+        <v>767700</v>
       </c>
       <c r="F60" s="3">
-        <v>402900</v>
+        <v>555000</v>
       </c>
       <c r="G60" s="3">
-        <v>580600</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
+        <v>381400</v>
+      </c>
+      <c r="H60" s="3">
+        <v>549600</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
@@ -2125,26 +2264,29 @@
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>272800</v>
+        <v>889000</v>
       </c>
       <c r="E61" s="3">
-        <v>310900</v>
+        <v>258200</v>
       </c>
       <c r="F61" s="3">
-        <v>383700</v>
+        <v>294300</v>
       </c>
       <c r="G61" s="3">
-        <v>374600</v>
+        <v>363200</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>354600</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2155,26 +2297,29 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>63500</v>
+        <v>136900</v>
       </c>
       <c r="E62" s="3">
-        <v>65600</v>
+        <v>60100</v>
       </c>
       <c r="F62" s="3">
-        <v>91900</v>
+        <v>62100</v>
       </c>
       <c r="G62" s="3">
-        <v>132600</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
+        <v>87000</v>
+      </c>
+      <c r="H62" s="3">
+        <v>125600</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2185,9 +2330,12 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2215,9 +2363,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2245,9 +2396,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2275,26 +2429,29 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1147400</v>
+        <v>1890500</v>
       </c>
       <c r="E66" s="3">
-        <v>963200</v>
+        <v>1086200</v>
       </c>
       <c r="F66" s="3">
-        <v>881900</v>
+        <v>911700</v>
       </c>
       <c r="G66" s="3">
-        <v>1101000</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
+        <v>834800</v>
+      </c>
+      <c r="H66" s="3">
+        <v>1042200</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
@@ -2305,9 +2462,12 @@
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2320,8 +2480,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2349,9 +2510,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2379,9 +2543,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2409,9 +2576,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2439,26 +2609,29 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1768000</v>
+        <v>1798900</v>
       </c>
       <c r="E72" s="3">
-        <v>1515600</v>
+        <v>1673500</v>
       </c>
       <c r="F72" s="3">
-        <v>1351700</v>
+        <v>1434600</v>
       </c>
       <c r="G72" s="3">
-        <v>1396200</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
+        <v>1279500</v>
+      </c>
+      <c r="H72" s="3">
+        <v>1321600</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
@@ -2469,9 +2642,12 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2499,9 +2675,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2529,9 +2708,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2559,26 +2741,29 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2233100</v>
+        <v>2281900</v>
       </c>
       <c r="E76" s="3">
-        <v>1972000</v>
+        <v>2113800</v>
       </c>
       <c r="F76" s="3">
-        <v>1959700</v>
+        <v>1866700</v>
       </c>
       <c r="G76" s="3">
-        <v>1987700</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
+        <v>1855000</v>
+      </c>
+      <c r="H76" s="3">
+        <v>1881600</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
@@ -2589,9 +2774,12 @@
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2619,32 +2807,35 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44651</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44286</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43921</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2654,26 +2845,29 @@
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>309600</v>
+        <v>210900</v>
       </c>
       <c r="E81" s="3">
-        <v>249600</v>
+        <v>293100</v>
       </c>
       <c r="F81" s="3">
-        <v>8600</v>
+        <v>236200</v>
       </c>
       <c r="G81" s="3">
-        <v>92800</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
+        <v>8100</v>
+      </c>
+      <c r="H81" s="3">
+        <v>87900</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>3</v>
@@ -2684,9 +2878,12 @@
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2699,25 +2896,26 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>86600</v>
+        <v>102200</v>
       </c>
       <c r="E83" s="3">
-        <v>92500</v>
+        <v>82000</v>
       </c>
       <c r="F83" s="3">
-        <v>112800</v>
+        <v>87500</v>
       </c>
       <c r="G83" s="3">
-        <v>129700</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
+        <v>106800</v>
+      </c>
+      <c r="H83" s="3">
+        <v>122700</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
@@ -2728,9 +2926,12 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2758,9 +2959,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2788,9 +2992,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2818,9 +3025,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2848,9 +3058,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2878,26 +3091,29 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>300600</v>
+        <v>420000</v>
       </c>
       <c r="E89" s="3">
-        <v>267300</v>
+        <v>284500</v>
       </c>
       <c r="F89" s="3">
-        <v>-42900</v>
+        <v>253000</v>
       </c>
       <c r="G89" s="3">
-        <v>259800</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
+        <v>-40600</v>
+      </c>
+      <c r="H89" s="3">
+        <v>245900</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
@@ -2908,9 +3124,12 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2923,25 +3142,26 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-33300</v>
+        <v>-34100</v>
       </c>
       <c r="E91" s="3">
-        <v>-40300</v>
+        <v>-31500</v>
       </c>
       <c r="F91" s="3">
-        <v>-49500</v>
+        <v>-38200</v>
       </c>
       <c r="G91" s="3">
-        <v>-67600</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
+        <v>-46900</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-64000</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
@@ -2952,9 +3172,12 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2982,9 +3205,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3012,26 +3238,29 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-15800</v>
+        <v>-724200</v>
       </c>
       <c r="E94" s="3">
-        <v>-59300</v>
+        <v>-15000</v>
       </c>
       <c r="F94" s="3">
-        <v>205400</v>
+        <v>-56100</v>
       </c>
       <c r="G94" s="3">
-        <v>-104200</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
+        <v>194400</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-98700</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
@@ -3042,9 +3271,12 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3057,25 +3289,26 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-59800</v>
+        <v>-87200</v>
       </c>
       <c r="E96" s="3">
-        <v>-63400</v>
+        <v>-56600</v>
       </c>
       <c r="F96" s="3">
-        <v>-47600</v>
+        <v>-60000</v>
       </c>
       <c r="G96" s="3">
-        <v>-63300</v>
+        <v>-45100</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-59900</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -3086,9 +3319,12 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3116,9 +3352,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3146,9 +3385,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3176,26 +3418,29 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-103500</v>
+        <v>509000</v>
       </c>
       <c r="E100" s="3">
-        <v>-242400</v>
+        <v>-98000</v>
       </c>
       <c r="F100" s="3">
-        <v>-212300</v>
+        <v>-229500</v>
       </c>
       <c r="G100" s="3">
-        <v>-73800</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
+        <v>-200900</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-69900</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
@@ -3206,26 +3451,29 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>1100</v>
+        <v>52300</v>
       </c>
       <c r="E101" s="3">
-        <v>20400</v>
+        <v>1000</v>
       </c>
       <c r="F101" s="3">
-        <v>22300</v>
+        <v>19300</v>
       </c>
       <c r="G101" s="3">
-        <v>-10600</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
+        <v>21100</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-10000</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
@@ -3236,26 +3484,29 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>182300</v>
+        <v>257100</v>
       </c>
       <c r="E102" s="3">
-        <v>-14000</v>
+        <v>172600</v>
       </c>
       <c r="F102" s="3">
-        <v>-27500</v>
+        <v>-13300</v>
       </c>
       <c r="G102" s="3">
-        <v>71100</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
+        <v>-26000</v>
+      </c>
+      <c r="H102" s="3">
+        <v>67300</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>3</v>
@@ -3266,7 +3517,10 @@
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SGAMY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SGAMY_YR_FIN.xlsx
@@ -715,19 +715,19 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2985200</v>
+        <v>3322100</v>
       </c>
       <c r="E8" s="3">
-        <v>2485900</v>
+        <v>2766400</v>
       </c>
       <c r="F8" s="3">
-        <v>2047700</v>
+        <v>2278700</v>
       </c>
       <c r="G8" s="3">
-        <v>1772000</v>
+        <v>1972000</v>
       </c>
       <c r="H8" s="3">
-        <v>2338900</v>
+        <v>2602800</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
@@ -748,19 +748,19 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1730000</v>
+        <v>1925200</v>
       </c>
       <c r="E9" s="3">
-        <v>1477400</v>
+        <v>1644100</v>
       </c>
       <c r="F9" s="3">
-        <v>1231900</v>
+        <v>1370900</v>
       </c>
       <c r="G9" s="3">
-        <v>1129100</v>
+        <v>1256500</v>
       </c>
       <c r="H9" s="3">
-        <v>1468000</v>
+        <v>1633700</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
@@ -781,19 +781,19 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1255200</v>
+        <v>1396800</v>
       </c>
       <c r="E10" s="3">
-        <v>1008500</v>
+        <v>1122300</v>
       </c>
       <c r="F10" s="3">
-        <v>815800</v>
+        <v>907900</v>
       </c>
       <c r="G10" s="3">
-        <v>642900</v>
+        <v>715500</v>
       </c>
       <c r="H10" s="3">
-        <v>870900</v>
+        <v>969200</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
@@ -829,19 +829,19 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>158600</v>
+        <v>176500</v>
       </c>
       <c r="E12" s="3">
-        <v>147000</v>
+        <v>163600</v>
       </c>
       <c r="F12" s="3">
-        <v>133600</v>
+        <v>148700</v>
       </c>
       <c r="G12" s="3">
-        <v>144200</v>
+        <v>160400</v>
       </c>
       <c r="H12" s="3">
-        <v>157700</v>
+        <v>175500</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>3</v>
@@ -895,19 +895,19 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>118400</v>
+        <v>131800</v>
       </c>
       <c r="E14" s="3">
-        <v>17200</v>
+        <v>19100</v>
       </c>
       <c r="F14" s="3">
-        <v>6700</v>
+        <v>7400</v>
       </c>
       <c r="G14" s="3">
-        <v>244900</v>
+        <v>272500</v>
       </c>
       <c r="H14" s="3">
-        <v>7900</v>
+        <v>8800</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -973,19 +973,19 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2741000</v>
+        <v>3050300</v>
       </c>
       <c r="E17" s="3">
-        <v>2204500</v>
+        <v>2453300</v>
       </c>
       <c r="F17" s="3">
-        <v>1849900</v>
+        <v>2058700</v>
       </c>
       <c r="G17" s="3">
-        <v>1975100</v>
+        <v>2198000</v>
       </c>
       <c r="H17" s="3">
-        <v>2170400</v>
+        <v>2415300</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>3</v>
@@ -1006,19 +1006,19 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>244200</v>
+        <v>271800</v>
       </c>
       <c r="E18" s="3">
-        <v>281300</v>
+        <v>313100</v>
       </c>
       <c r="F18" s="3">
-        <v>197800</v>
+        <v>220100</v>
       </c>
       <c r="G18" s="3">
-        <v>-203000</v>
+        <v>-226000</v>
       </c>
       <c r="H18" s="3">
-        <v>168500</v>
+        <v>187500</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
@@ -1054,19 +1054,19 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>27600</v>
+        <v>30700</v>
       </c>
       <c r="E20" s="3">
-        <v>21000</v>
+        <v>23400</v>
       </c>
       <c r="F20" s="3">
-        <v>46100</v>
+        <v>51300</v>
       </c>
       <c r="G20" s="3">
-        <v>143200</v>
+        <v>159400</v>
       </c>
       <c r="H20" s="3">
-        <v>7500</v>
+        <v>8300</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
@@ -1087,19 +1087,19 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>373800</v>
+        <v>415300</v>
       </c>
       <c r="E21" s="3">
-        <v>384200</v>
+        <v>427000</v>
       </c>
       <c r="F21" s="3">
-        <v>331200</v>
+        <v>368100</v>
       </c>
       <c r="G21" s="3">
-        <v>46800</v>
+        <v>51400</v>
       </c>
       <c r="H21" s="3">
-        <v>298500</v>
+        <v>331400</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
@@ -1120,19 +1120,19 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>4900</v>
+        <v>5400</v>
       </c>
       <c r="E22" s="3">
-        <v>2000</v>
+        <v>2300</v>
       </c>
       <c r="F22" s="3">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="G22" s="3">
-        <v>3000</v>
+        <v>3300</v>
       </c>
       <c r="H22" s="3">
-        <v>3000</v>
+        <v>3400</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
@@ -1153,19 +1153,19 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>266900</v>
+        <v>297000</v>
       </c>
       <c r="E23" s="3">
-        <v>300300</v>
+        <v>334200</v>
       </c>
       <c r="F23" s="3">
-        <v>241900</v>
+        <v>269200</v>
       </c>
       <c r="G23" s="3">
-        <v>-62800</v>
+        <v>-69900</v>
       </c>
       <c r="H23" s="3">
-        <v>172900</v>
+        <v>192400</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>3</v>
@@ -1186,19 +1186,19 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>55500</v>
+        <v>61800</v>
       </c>
       <c r="E24" s="3">
-        <v>7200</v>
+        <v>8100</v>
       </c>
       <c r="F24" s="3">
-        <v>5800</v>
+        <v>6400</v>
       </c>
       <c r="G24" s="3">
-        <v>-74800</v>
+        <v>-83200</v>
       </c>
       <c r="H24" s="3">
-        <v>83800</v>
+        <v>93200</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
@@ -1252,19 +1252,19 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>211400</v>
+        <v>235200</v>
       </c>
       <c r="E26" s="3">
-        <v>293100</v>
+        <v>326100</v>
       </c>
       <c r="F26" s="3">
-        <v>236200</v>
+        <v>262800</v>
       </c>
       <c r="G26" s="3">
-        <v>12000</v>
+        <v>13300</v>
       </c>
       <c r="H26" s="3">
-        <v>89100</v>
+        <v>99200</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>3</v>
@@ -1285,19 +1285,19 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>210900</v>
+        <v>234700</v>
       </c>
       <c r="E27" s="3">
-        <v>293100</v>
+        <v>326200</v>
       </c>
       <c r="F27" s="3">
-        <v>236200</v>
+        <v>262900</v>
       </c>
       <c r="G27" s="3">
-        <v>8100</v>
+        <v>9000</v>
       </c>
       <c r="H27" s="3">
-        <v>87900</v>
+        <v>97800</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>3</v>
@@ -1450,19 +1450,19 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-27600</v>
+        <v>-30700</v>
       </c>
       <c r="E32" s="3">
-        <v>-21000</v>
+        <v>-23400</v>
       </c>
       <c r="F32" s="3">
-        <v>-46100</v>
+        <v>-51300</v>
       </c>
       <c r="G32" s="3">
-        <v>-143200</v>
+        <v>-159400</v>
       </c>
       <c r="H32" s="3">
-        <v>-7500</v>
+        <v>-8300</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
@@ -1483,19 +1483,19 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>210900</v>
+        <v>234700</v>
       </c>
       <c r="E33" s="3">
-        <v>293100</v>
+        <v>326200</v>
       </c>
       <c r="F33" s="3">
-        <v>236200</v>
+        <v>262900</v>
       </c>
       <c r="G33" s="3">
-        <v>8100</v>
+        <v>9000</v>
       </c>
       <c r="H33" s="3">
-        <v>87900</v>
+        <v>97800</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>3</v>
@@ -1549,19 +1549,19 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>210900</v>
+        <v>234700</v>
       </c>
       <c r="E35" s="3">
-        <v>293100</v>
+        <v>326200</v>
       </c>
       <c r="F35" s="3">
-        <v>236200</v>
+        <v>262900</v>
       </c>
       <c r="G35" s="3">
-        <v>8100</v>
+        <v>9000</v>
       </c>
       <c r="H35" s="3">
-        <v>87900</v>
+        <v>97800</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>3</v>
@@ -1650,19 +1650,19 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1350700</v>
+        <v>1503200</v>
       </c>
       <c r="E41" s="3">
-        <v>1145300</v>
+        <v>1274500</v>
       </c>
       <c r="F41" s="3">
-        <v>972700</v>
+        <v>1082500</v>
       </c>
       <c r="G41" s="3">
-        <v>988700</v>
+        <v>1100300</v>
       </c>
       <c r="H41" s="3">
-        <v>1014500</v>
+        <v>1129000</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
@@ -1683,7 +1683,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>51600</v>
+        <v>57500</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>3</v>
@@ -1692,10 +1692,10 @@
         <v>3</v>
       </c>
       <c r="G42" s="3">
-        <v>4600</v>
+        <v>5100</v>
       </c>
       <c r="H42" s="3">
-        <v>34400</v>
+        <v>38300</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>3</v>
@@ -1716,19 +1716,19 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>473800</v>
+        <v>527300</v>
       </c>
       <c r="E43" s="3">
-        <v>438200</v>
+        <v>487700</v>
       </c>
       <c r="F43" s="3">
-        <v>321800</v>
+        <v>358100</v>
       </c>
       <c r="G43" s="3">
-        <v>307800</v>
+        <v>342500</v>
       </c>
       <c r="H43" s="3">
-        <v>286700</v>
+        <v>319100</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
@@ -1749,19 +1749,19 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>521600</v>
+        <v>580500</v>
       </c>
       <c r="E44" s="3">
-        <v>570800</v>
+        <v>635200</v>
       </c>
       <c r="F44" s="3">
-        <v>430800</v>
+        <v>479400</v>
       </c>
       <c r="G44" s="3">
-        <v>337600</v>
+        <v>375700</v>
       </c>
       <c r="H44" s="3">
-        <v>299900</v>
+        <v>333700</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
@@ -1782,19 +1782,19 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>122300</v>
+        <v>136100</v>
       </c>
       <c r="E45" s="3">
-        <v>103400</v>
+        <v>115100</v>
       </c>
       <c r="F45" s="3">
-        <v>110800</v>
+        <v>123300</v>
       </c>
       <c r="G45" s="3">
-        <v>124100</v>
+        <v>138100</v>
       </c>
       <c r="H45" s="3">
-        <v>80500</v>
+        <v>89600</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -1815,19 +1815,19 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2520100</v>
+        <v>2804500</v>
       </c>
       <c r="E46" s="3">
-        <v>2257600</v>
+        <v>2512400</v>
       </c>
       <c r="F46" s="3">
-        <v>1836100</v>
+        <v>2043300</v>
       </c>
       <c r="G46" s="3">
-        <v>1762800</v>
+        <v>1961700</v>
       </c>
       <c r="H46" s="3">
-        <v>1716100</v>
+        <v>1909700</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
@@ -1848,19 +1848,19 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>366900</v>
+        <v>408400</v>
       </c>
       <c r="E47" s="3">
-        <v>251400</v>
+        <v>279800</v>
       </c>
       <c r="F47" s="3">
-        <v>259900</v>
+        <v>289300</v>
       </c>
       <c r="G47" s="3">
-        <v>244300</v>
+        <v>271900</v>
       </c>
       <c r="H47" s="3">
-        <v>355400</v>
+        <v>395600</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
@@ -1881,19 +1881,19 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>383400</v>
+        <v>426700</v>
       </c>
       <c r="E48" s="3">
-        <v>385900</v>
+        <v>429400</v>
       </c>
       <c r="F48" s="3">
-        <v>385100</v>
+        <v>428500</v>
       </c>
       <c r="G48" s="3">
-        <v>393100</v>
+        <v>437500</v>
       </c>
       <c r="H48" s="3">
-        <v>552800</v>
+        <v>615200</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
@@ -1914,19 +1914,19 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>588800</v>
+        <v>655200</v>
       </c>
       <c r="E49" s="3">
-        <v>84500</v>
+        <v>94100</v>
       </c>
       <c r="F49" s="3">
-        <v>84100</v>
+        <v>93600</v>
       </c>
       <c r="G49" s="3">
-        <v>95700</v>
+        <v>106500</v>
       </c>
       <c r="H49" s="3">
-        <v>114600</v>
+        <v>127600</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
@@ -2013,19 +2013,19 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>313200</v>
+        <v>348600</v>
       </c>
       <c r="E52" s="3">
-        <v>220600</v>
+        <v>245500</v>
       </c>
       <c r="F52" s="3">
-        <v>213200</v>
+        <v>237300</v>
       </c>
       <c r="G52" s="3">
-        <v>193900</v>
+        <v>215800</v>
       </c>
       <c r="H52" s="3">
-        <v>184800</v>
+        <v>205600</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -2079,19 +2079,19 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>4172500</v>
+        <v>4643400</v>
       </c>
       <c r="E54" s="3">
-        <v>3200000</v>
+        <v>3561100</v>
       </c>
       <c r="F54" s="3">
-        <v>2778400</v>
+        <v>3092000</v>
       </c>
       <c r="G54" s="3">
-        <v>2689800</v>
+        <v>2993400</v>
       </c>
       <c r="H54" s="3">
-        <v>2923700</v>
+        <v>3253700</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
@@ -2142,19 +2142,19 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>166400</v>
+        <v>185200</v>
       </c>
       <c r="E57" s="3">
-        <v>194900</v>
+        <v>216900</v>
       </c>
       <c r="F57" s="3">
-        <v>156000</v>
+        <v>173600</v>
       </c>
       <c r="G57" s="3">
-        <v>108400</v>
+        <v>120700</v>
       </c>
       <c r="H57" s="3">
-        <v>113800</v>
+        <v>126600</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
@@ -2175,19 +2175,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>143600</v>
+        <v>173400</v>
       </c>
       <c r="E58" s="3">
-        <v>117400</v>
+        <v>130700</v>
       </c>
       <c r="F58" s="3">
-        <v>71200</v>
+        <v>79200</v>
       </c>
       <c r="G58" s="3">
-        <v>7400</v>
+        <v>8300</v>
       </c>
       <c r="H58" s="3">
-        <v>154700</v>
+        <v>172200</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
@@ -2208,19 +2208,19 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>554400</v>
+        <v>603400</v>
       </c>
       <c r="E59" s="3">
-        <v>455300</v>
+        <v>506700</v>
       </c>
       <c r="F59" s="3">
-        <v>327800</v>
+        <v>364800</v>
       </c>
       <c r="G59" s="3">
-        <v>265500</v>
+        <v>295500</v>
       </c>
       <c r="H59" s="3">
-        <v>281100</v>
+        <v>312800</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
@@ -2241,19 +2241,19 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>864500</v>
+        <v>962000</v>
       </c>
       <c r="E60" s="3">
-        <v>767700</v>
+        <v>854400</v>
       </c>
       <c r="F60" s="3">
-        <v>555000</v>
+        <v>617600</v>
       </c>
       <c r="G60" s="3">
-        <v>381400</v>
+        <v>424400</v>
       </c>
       <c r="H60" s="3">
-        <v>549600</v>
+        <v>611600</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
@@ -2274,19 +2274,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>889000</v>
+        <v>990000</v>
       </c>
       <c r="E61" s="3">
-        <v>258200</v>
+        <v>287300</v>
       </c>
       <c r="F61" s="3">
-        <v>294300</v>
+        <v>327500</v>
       </c>
       <c r="G61" s="3">
-        <v>363200</v>
+        <v>404200</v>
       </c>
       <c r="H61" s="3">
-        <v>354600</v>
+        <v>394600</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2307,19 +2307,19 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>136900</v>
+        <v>151600</v>
       </c>
       <c r="E62" s="3">
-        <v>60100</v>
+        <v>66900</v>
       </c>
       <c r="F62" s="3">
-        <v>62100</v>
+        <v>69200</v>
       </c>
       <c r="G62" s="3">
-        <v>87000</v>
+        <v>96800</v>
       </c>
       <c r="H62" s="3">
-        <v>125600</v>
+        <v>139700</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2439,19 +2439,19 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1890500</v>
+        <v>2103900</v>
       </c>
       <c r="E66" s="3">
-        <v>1086200</v>
+        <v>1208700</v>
       </c>
       <c r="F66" s="3">
-        <v>911700</v>
+        <v>1014600</v>
       </c>
       <c r="G66" s="3">
-        <v>834800</v>
+        <v>929000</v>
       </c>
       <c r="H66" s="3">
-        <v>1042200</v>
+        <v>1159800</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
@@ -2619,19 +2619,19 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1798900</v>
+        <v>2001900</v>
       </c>
       <c r="E72" s="3">
-        <v>1673500</v>
+        <v>1862400</v>
       </c>
       <c r="F72" s="3">
-        <v>1434600</v>
+        <v>1596500</v>
       </c>
       <c r="G72" s="3">
-        <v>1279500</v>
+        <v>1423900</v>
       </c>
       <c r="H72" s="3">
-        <v>1321600</v>
+        <v>1470700</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
@@ -2751,19 +2751,19 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2281900</v>
+        <v>2539500</v>
       </c>
       <c r="E76" s="3">
-        <v>2113800</v>
+        <v>2352400</v>
       </c>
       <c r="F76" s="3">
-        <v>1866700</v>
+        <v>2077400</v>
       </c>
       <c r="G76" s="3">
-        <v>1855000</v>
+        <v>2064400</v>
       </c>
       <c r="H76" s="3">
-        <v>1881600</v>
+        <v>2093900</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
@@ -2855,19 +2855,19 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>210900</v>
+        <v>234700</v>
       </c>
       <c r="E81" s="3">
-        <v>293100</v>
+        <v>326200</v>
       </c>
       <c r="F81" s="3">
-        <v>236200</v>
+        <v>262900</v>
       </c>
       <c r="G81" s="3">
-        <v>8100</v>
+        <v>9000</v>
       </c>
       <c r="H81" s="3">
-        <v>87900</v>
+        <v>97800</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>3</v>
@@ -2903,19 +2903,19 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>102200</v>
+        <v>113700</v>
       </c>
       <c r="E83" s="3">
-        <v>82000</v>
+        <v>91200</v>
       </c>
       <c r="F83" s="3">
-        <v>87500</v>
+        <v>97400</v>
       </c>
       <c r="G83" s="3">
-        <v>106800</v>
+        <v>118800</v>
       </c>
       <c r="H83" s="3">
-        <v>122700</v>
+        <v>136600</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
@@ -3101,19 +3101,19 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>420000</v>
+        <v>467400</v>
       </c>
       <c r="E89" s="3">
-        <v>284500</v>
+        <v>316600</v>
       </c>
       <c r="F89" s="3">
-        <v>253000</v>
+        <v>281500</v>
       </c>
       <c r="G89" s="3">
-        <v>-40600</v>
+        <v>-45200</v>
       </c>
       <c r="H89" s="3">
-        <v>245900</v>
+        <v>273700</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
@@ -3149,19 +3149,19 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-34100</v>
+        <v>-37900</v>
       </c>
       <c r="E91" s="3">
-        <v>-31500</v>
+        <v>-35100</v>
       </c>
       <c r="F91" s="3">
-        <v>-38200</v>
+        <v>-42500</v>
       </c>
       <c r="G91" s="3">
-        <v>-46900</v>
+        <v>-52200</v>
       </c>
       <c r="H91" s="3">
-        <v>-64000</v>
+        <v>-71300</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
@@ -3248,19 +3248,19 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-724200</v>
+        <v>-805900</v>
       </c>
       <c r="E94" s="3">
-        <v>-15000</v>
+        <v>-16700</v>
       </c>
       <c r="F94" s="3">
-        <v>-56100</v>
+        <v>-62400</v>
       </c>
       <c r="G94" s="3">
-        <v>194400</v>
+        <v>216400</v>
       </c>
       <c r="H94" s="3">
-        <v>-98700</v>
+        <v>-109800</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
@@ -3296,19 +3296,19 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-87200</v>
+        <v>-97100</v>
       </c>
       <c r="E96" s="3">
-        <v>-56600</v>
+        <v>-62900</v>
       </c>
       <c r="F96" s="3">
-        <v>-60000</v>
+        <v>-66800</v>
       </c>
       <c r="G96" s="3">
-        <v>-45100</v>
+        <v>-50100</v>
       </c>
       <c r="H96" s="3">
-        <v>-59900</v>
+        <v>-66700</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -3428,19 +3428,19 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>509000</v>
+        <v>566500</v>
       </c>
       <c r="E100" s="3">
-        <v>-98000</v>
+        <v>-109000</v>
       </c>
       <c r="F100" s="3">
-        <v>-229500</v>
+        <v>-255400</v>
       </c>
       <c r="G100" s="3">
-        <v>-200900</v>
+        <v>-223600</v>
       </c>
       <c r="H100" s="3">
-        <v>-69900</v>
+        <v>-77800</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
@@ -3461,19 +3461,19 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>52300</v>
+        <v>58200</v>
       </c>
       <c r="E101" s="3">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="F101" s="3">
-        <v>19300</v>
+        <v>21500</v>
       </c>
       <c r="G101" s="3">
-        <v>21100</v>
+        <v>23500</v>
       </c>
       <c r="H101" s="3">
-        <v>-10000</v>
+        <v>-11200</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
@@ -3494,19 +3494,19 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>257100</v>
+        <v>286100</v>
       </c>
       <c r="E102" s="3">
-        <v>172600</v>
+        <v>192100</v>
       </c>
       <c r="F102" s="3">
-        <v>-13300</v>
+        <v>-14800</v>
       </c>
       <c r="G102" s="3">
-        <v>-26000</v>
+        <v>-29000</v>
       </c>
       <c r="H102" s="3">
-        <v>67300</v>
+        <v>74900</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/SGAMY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SGAMY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
   <si>
     <t>SGAMY</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -696,11 +696,11 @@
       <c r="H7" s="2">
         <v>43921</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
+      <c r="I7" s="2">
+        <v>43555</v>
+      </c>
+      <c r="J7" s="2">
+        <v>43190</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
@@ -715,25 +715,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>3322100</v>
+        <v>3093400</v>
       </c>
       <c r="E8" s="3">
-        <v>2766400</v>
+        <v>2931000</v>
       </c>
       <c r="F8" s="3">
-        <v>2278700</v>
+        <v>2643000</v>
       </c>
       <c r="G8" s="3">
-        <v>1972000</v>
+        <v>2511300</v>
       </c>
       <c r="H8" s="3">
-        <v>2602800</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+        <v>3406900</v>
+      </c>
+      <c r="I8" s="3">
+        <v>2992900</v>
+      </c>
+      <c r="J8" s="3">
+        <v>3047500</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -748,25 +748,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1925200</v>
+        <v>1792700</v>
       </c>
       <c r="E9" s="3">
-        <v>1644100</v>
+        <v>1742000</v>
       </c>
       <c r="F9" s="3">
-        <v>1370900</v>
+        <v>1590000</v>
       </c>
       <c r="G9" s="3">
-        <v>1256500</v>
+        <v>1600100</v>
       </c>
       <c r="H9" s="3">
-        <v>1633700</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+        <v>2138400</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1906000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1910700</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -781,25 +781,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1396800</v>
+        <v>1300700</v>
       </c>
       <c r="E10" s="3">
-        <v>1122300</v>
+        <v>1189100</v>
       </c>
       <c r="F10" s="3">
-        <v>907900</v>
+        <v>1053000</v>
       </c>
       <c r="G10" s="3">
-        <v>715500</v>
+        <v>911200</v>
       </c>
       <c r="H10" s="3">
-        <v>969200</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>1268600</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1087000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1136800</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -829,25 +829,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>176500</v>
+        <v>164400</v>
       </c>
       <c r="E12" s="3">
-        <v>163600</v>
+        <v>173400</v>
       </c>
       <c r="F12" s="3">
-        <v>148700</v>
+        <v>172400</v>
       </c>
       <c r="G12" s="3">
-        <v>160400</v>
+        <v>204300</v>
       </c>
       <c r="H12" s="3">
-        <v>175500</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+        <v>229700</v>
+      </c>
+      <c r="I12" s="3">
+        <v>209800</v>
+      </c>
+      <c r="J12" s="3">
+        <v>217800</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -895,25 +895,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>131800</v>
+        <v>119600</v>
       </c>
       <c r="E14" s="3">
-        <v>19100</v>
+        <v>20200</v>
       </c>
       <c r="F14" s="3">
-        <v>7400</v>
+        <v>-33800</v>
       </c>
       <c r="G14" s="3">
-        <v>272500</v>
+        <v>107200</v>
       </c>
       <c r="H14" s="3">
-        <v>8800</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+        <v>-15000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>5700</v>
+      </c>
+      <c r="J14" s="3">
+        <v>25700</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -928,25 +928,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>105900</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>96600</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>113000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>151300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>178800</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>188500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>201000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -973,25 +973,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3050300</v>
+        <v>2717700</v>
       </c>
       <c r="E17" s="3">
-        <v>2453300</v>
+        <v>2579100</v>
       </c>
       <c r="F17" s="3">
-        <v>2058700</v>
+        <v>2379100</v>
       </c>
       <c r="G17" s="3">
-        <v>2198000</v>
+        <v>2452000</v>
       </c>
       <c r="H17" s="3">
-        <v>2415300</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+        <v>3150000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>2874900</v>
+      </c>
+      <c r="J17" s="3">
+        <v>2880700</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1006,25 +1006,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>271800</v>
+        <v>375800</v>
       </c>
       <c r="E18" s="3">
-        <v>313100</v>
+        <v>352000</v>
       </c>
       <c r="F18" s="3">
-        <v>220100</v>
+        <v>263900</v>
       </c>
       <c r="G18" s="3">
-        <v>-226000</v>
+        <v>59300</v>
       </c>
       <c r="H18" s="3">
-        <v>187500</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>256900</v>
+      </c>
+      <c r="I18" s="3">
+        <v>118000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>166900</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1054,25 +1054,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>30700</v>
+        <v>-2000</v>
       </c>
       <c r="E20" s="3">
-        <v>23400</v>
+        <v>-3100</v>
       </c>
       <c r="F20" s="3">
-        <v>51300</v>
+        <v>13100</v>
       </c>
       <c r="G20" s="3">
-        <v>159400</v>
+        <v>54000</v>
       </c>
       <c r="H20" s="3">
-        <v>8300</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+        <v>27700</v>
+      </c>
+      <c r="I20" s="3">
+        <v>55600</v>
+      </c>
+      <c r="J20" s="3">
+        <v>38300</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1087,25 +1087,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>415300</v>
+        <v>483700</v>
       </c>
       <c r="E21" s="3">
-        <v>427000</v>
+        <v>451700</v>
       </c>
       <c r="F21" s="3">
-        <v>368100</v>
+        <v>363700</v>
       </c>
       <c r="G21" s="3">
-        <v>51400</v>
+        <v>156600</v>
       </c>
       <c r="H21" s="3">
-        <v>331400</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>408000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>250900</v>
+      </c>
+      <c r="J21" s="3">
+        <v>329600</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1120,25 +1120,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>5400</v>
+        <v>5100</v>
       </c>
       <c r="E22" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="F22" s="3">
-        <v>2100</v>
+        <v>2500</v>
       </c>
       <c r="G22" s="3">
-        <v>3300</v>
+        <v>4200</v>
       </c>
       <c r="H22" s="3">
-        <v>3400</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+        <v>4400</v>
+      </c>
+      <c r="I22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="J22" s="3">
+        <v>6700</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1153,25 +1153,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>297000</v>
+        <v>276600</v>
       </c>
       <c r="E23" s="3">
-        <v>334200</v>
+        <v>354100</v>
       </c>
       <c r="F23" s="3">
-        <v>269200</v>
+        <v>312300</v>
       </c>
       <c r="G23" s="3">
-        <v>-69900</v>
+        <v>-89000</v>
       </c>
       <c r="H23" s="3">
-        <v>192400</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+        <v>251900</v>
+      </c>
+      <c r="I23" s="3">
+        <v>63000</v>
+      </c>
+      <c r="J23" s="3">
+        <v>116900</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1186,25 +1186,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>61800</v>
+        <v>57500</v>
       </c>
       <c r="E24" s="3">
-        <v>8100</v>
+        <v>8500</v>
       </c>
       <c r="F24" s="3">
-        <v>6400</v>
+        <v>7400</v>
       </c>
       <c r="G24" s="3">
-        <v>-83200</v>
+        <v>-106000</v>
       </c>
       <c r="H24" s="3">
-        <v>93200</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+        <v>122000</v>
+      </c>
+      <c r="I24" s="3">
+        <v>38400</v>
+      </c>
+      <c r="J24" s="3">
+        <v>28700</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1252,25 +1252,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>235200</v>
+        <v>219000</v>
       </c>
       <c r="E26" s="3">
-        <v>326100</v>
+        <v>345500</v>
       </c>
       <c r="F26" s="3">
-        <v>262800</v>
+        <v>304800</v>
       </c>
       <c r="G26" s="3">
-        <v>13300</v>
+        <v>17000</v>
       </c>
       <c r="H26" s="3">
-        <v>99200</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+        <v>129800</v>
+      </c>
+      <c r="I26" s="3">
+        <v>24600</v>
+      </c>
+      <c r="J26" s="3">
+        <v>88200</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1285,25 +1285,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>234700</v>
+        <v>218500</v>
       </c>
       <c r="E27" s="3">
-        <v>326200</v>
+        <v>345600</v>
       </c>
       <c r="F27" s="3">
-        <v>262900</v>
+        <v>304900</v>
       </c>
       <c r="G27" s="3">
-        <v>9000</v>
+        <v>11500</v>
       </c>
       <c r="H27" s="3">
-        <v>97800</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+        <v>128000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>23800</v>
+      </c>
+      <c r="J27" s="3">
+        <v>84100</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1450,25 +1450,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-30700</v>
+        <v>2000</v>
       </c>
       <c r="E32" s="3">
-        <v>-23400</v>
+        <v>3100</v>
       </c>
       <c r="F32" s="3">
-        <v>-51300</v>
+        <v>-13100</v>
       </c>
       <c r="G32" s="3">
-        <v>-159400</v>
+        <v>-54000</v>
       </c>
       <c r="H32" s="3">
-        <v>-8300</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+        <v>-27700</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-55600</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-38300</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1483,25 +1483,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>234700</v>
+        <v>218500</v>
       </c>
       <c r="E33" s="3">
-        <v>326200</v>
+        <v>345600</v>
       </c>
       <c r="F33" s="3">
-        <v>262900</v>
+        <v>304900</v>
       </c>
       <c r="G33" s="3">
-        <v>9000</v>
+        <v>11500</v>
       </c>
       <c r="H33" s="3">
-        <v>97800</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+        <v>128000</v>
+      </c>
+      <c r="I33" s="3">
+        <v>23800</v>
+      </c>
+      <c r="J33" s="3">
+        <v>84100</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1549,25 +1549,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>234700</v>
+        <v>218500</v>
       </c>
       <c r="E35" s="3">
-        <v>326200</v>
+        <v>345600</v>
       </c>
       <c r="F35" s="3">
-        <v>262900</v>
+        <v>304900</v>
       </c>
       <c r="G35" s="3">
-        <v>9000</v>
+        <v>11500</v>
       </c>
       <c r="H35" s="3">
-        <v>97800</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+        <v>128000</v>
+      </c>
+      <c r="I35" s="3">
+        <v>23800</v>
+      </c>
+      <c r="J35" s="3">
+        <v>84100</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1601,11 +1601,11 @@
       <c r="H38" s="2">
         <v>43921</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
+      <c r="I38" s="2">
+        <v>43555</v>
+      </c>
+      <c r="J38" s="2">
+        <v>43190</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
@@ -1650,25 +1650,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1503200</v>
+        <v>1399700</v>
       </c>
       <c r="E41" s="3">
-        <v>1274500</v>
+        <v>1350400</v>
       </c>
       <c r="F41" s="3">
-        <v>1082500</v>
+        <v>1255500</v>
       </c>
       <c r="G41" s="3">
-        <v>1100300</v>
+        <v>1401200</v>
       </c>
       <c r="H41" s="3">
-        <v>1129000</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+        <v>1477800</v>
+      </c>
+      <c r="I41" s="3">
+        <v>1240200</v>
+      </c>
+      <c r="J41" s="3">
+        <v>1486700</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1683,25 +1683,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>57500</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
+        <v>53500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>5100</v>
+        <v>6500</v>
       </c>
       <c r="H42" s="3">
-        <v>38300</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+        <v>50200</v>
+      </c>
+      <c r="I42" s="3">
+        <v>130900</v>
+      </c>
+      <c r="J42" s="3">
+        <v>232500</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1716,25 +1716,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>527300</v>
+        <v>491000</v>
       </c>
       <c r="E43" s="3">
-        <v>487700</v>
+        <v>516700</v>
       </c>
       <c r="F43" s="3">
-        <v>358100</v>
+        <v>415400</v>
       </c>
       <c r="G43" s="3">
-        <v>342500</v>
+        <v>436200</v>
       </c>
       <c r="H43" s="3">
-        <v>319100</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>417700</v>
+      </c>
+      <c r="I43" s="3">
+        <v>392500</v>
+      </c>
+      <c r="J43" s="3">
+        <v>315700</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1749,25 +1749,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>580500</v>
+        <v>540500</v>
       </c>
       <c r="E44" s="3">
-        <v>635200</v>
+        <v>673000</v>
       </c>
       <c r="F44" s="3">
-        <v>479400</v>
+        <v>556100</v>
       </c>
       <c r="G44" s="3">
-        <v>375700</v>
+        <v>478400</v>
       </c>
       <c r="H44" s="3">
-        <v>333700</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+        <v>436900</v>
+      </c>
+      <c r="I44" s="3">
+        <v>451400</v>
+      </c>
+      <c r="J44" s="3">
+        <v>382000</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -1782,25 +1782,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>136100</v>
+        <v>126700</v>
       </c>
       <c r="E45" s="3">
-        <v>115100</v>
+        <v>121900</v>
       </c>
       <c r="F45" s="3">
-        <v>123300</v>
+        <v>143000</v>
       </c>
       <c r="G45" s="3">
-        <v>138100</v>
+        <v>175800</v>
       </c>
       <c r="H45" s="3">
-        <v>89600</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+        <v>117200</v>
+      </c>
+      <c r="I45" s="3">
+        <v>135600</v>
+      </c>
+      <c r="J45" s="3">
+        <v>147200</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -1815,25 +1815,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2804500</v>
+        <v>2611500</v>
       </c>
       <c r="E46" s="3">
-        <v>2512400</v>
+        <v>2661900</v>
       </c>
       <c r="F46" s="3">
-        <v>2043300</v>
+        <v>2369900</v>
       </c>
       <c r="G46" s="3">
-        <v>1961700</v>
+        <v>2498200</v>
       </c>
       <c r="H46" s="3">
-        <v>1909700</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+        <v>2499700</v>
+      </c>
+      <c r="I46" s="3">
+        <v>2350500</v>
+      </c>
+      <c r="J46" s="3">
+        <v>2611500</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -1848,25 +1848,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>408400</v>
+        <v>531900</v>
       </c>
       <c r="E47" s="3">
-        <v>279800</v>
+        <v>430500</v>
       </c>
       <c r="F47" s="3">
-        <v>289300</v>
+        <v>496500</v>
       </c>
       <c r="G47" s="3">
-        <v>271900</v>
+        <v>497600</v>
       </c>
       <c r="H47" s="3">
-        <v>395600</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+        <v>765200</v>
+      </c>
+      <c r="I47" s="3">
+        <v>900300</v>
+      </c>
+      <c r="J47" s="3">
+        <v>862200</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -1881,25 +1881,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>426700</v>
+        <v>397300</v>
       </c>
       <c r="E48" s="3">
-        <v>429400</v>
+        <v>455000</v>
       </c>
       <c r="F48" s="3">
-        <v>428500</v>
+        <v>497000</v>
       </c>
       <c r="G48" s="3">
-        <v>437500</v>
+        <v>557100</v>
       </c>
       <c r="H48" s="3">
-        <v>615200</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+        <v>805300</v>
+      </c>
+      <c r="I48" s="3">
+        <v>758200</v>
+      </c>
+      <c r="J48" s="3">
+        <v>735800</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -1914,25 +1914,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>655200</v>
+        <v>610100</v>
       </c>
       <c r="E49" s="3">
-        <v>94100</v>
+        <v>99700</v>
       </c>
       <c r="F49" s="3">
-        <v>93600</v>
+        <v>108600</v>
       </c>
       <c r="G49" s="3">
-        <v>106500</v>
+        <v>135600</v>
       </c>
       <c r="H49" s="3">
-        <v>127600</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>167000</v>
+      </c>
+      <c r="I49" s="3">
+        <v>138000</v>
+      </c>
+      <c r="J49" s="3">
+        <v>221100</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2013,25 +2013,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>348600</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
-        <v>245500</v>
+        <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>237300</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
-        <v>215800</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>205600</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2079,25 +2079,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>4643400</v>
+        <v>4323800</v>
       </c>
       <c r="E54" s="3">
-        <v>3561100</v>
+        <v>3773000</v>
       </c>
       <c r="F54" s="3">
-        <v>3092000</v>
+        <v>3586200</v>
       </c>
       <c r="G54" s="3">
-        <v>2993400</v>
+        <v>3812000</v>
       </c>
       <c r="H54" s="3">
-        <v>3253700</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+        <v>4258900</v>
+      </c>
+      <c r="I54" s="3">
+        <v>4193200</v>
+      </c>
+      <c r="J54" s="3">
+        <v>4458400</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2142,25 +2142,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>185200</v>
+        <v>172500</v>
       </c>
       <c r="E57" s="3">
-        <v>216900</v>
+        <v>229900</v>
       </c>
       <c r="F57" s="3">
-        <v>173600</v>
+        <v>201400</v>
       </c>
       <c r="G57" s="3">
-        <v>120700</v>
+        <v>153700</v>
       </c>
       <c r="H57" s="3">
-        <v>126600</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+        <v>165700</v>
+      </c>
+      <c r="I57" s="3">
+        <v>223400</v>
+      </c>
+      <c r="J57" s="3">
+        <v>204500</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2175,25 +2175,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>173400</v>
+        <v>148800</v>
       </c>
       <c r="E58" s="3">
-        <v>130700</v>
+        <v>127900</v>
       </c>
       <c r="F58" s="3">
-        <v>79200</v>
+        <v>82300</v>
       </c>
       <c r="G58" s="3">
-        <v>8300</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>172200</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>216800</v>
+      </c>
+      <c r="I58" s="3">
+        <v>233300</v>
+      </c>
+      <c r="J58" s="3">
+        <v>243300</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2208,25 +2208,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>603400</v>
+        <v>333200</v>
       </c>
       <c r="E59" s="3">
-        <v>506700</v>
+        <v>316200</v>
       </c>
       <c r="F59" s="3">
-        <v>364800</v>
+        <v>186100</v>
       </c>
       <c r="G59" s="3">
-        <v>295500</v>
+        <v>162400</v>
       </c>
       <c r="H59" s="3">
-        <v>312800</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>194600</v>
+      </c>
+      <c r="I59" s="3">
+        <v>138700</v>
+      </c>
+      <c r="J59" s="3">
+        <v>164200</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2241,25 +2241,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>962000</v>
+        <v>895800</v>
       </c>
       <c r="E60" s="3">
-        <v>854400</v>
+        <v>905200</v>
       </c>
       <c r="F60" s="3">
-        <v>617600</v>
+        <v>716300</v>
       </c>
       <c r="G60" s="3">
-        <v>424400</v>
+        <v>540500</v>
       </c>
       <c r="H60" s="3">
-        <v>611600</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+        <v>800600</v>
+      </c>
+      <c r="I60" s="3">
+        <v>790000</v>
+      </c>
+      <c r="J60" s="3">
+        <v>795500</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2274,25 +2274,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>990000</v>
+        <v>921200</v>
       </c>
       <c r="E61" s="3">
-        <v>287300</v>
+        <v>303500</v>
       </c>
       <c r="F61" s="3">
-        <v>327500</v>
+        <v>378900</v>
       </c>
       <c r="G61" s="3">
-        <v>404200</v>
+        <v>513600</v>
       </c>
       <c r="H61" s="3">
-        <v>394600</v>
+        <v>483300</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>454200</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>575900</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2307,25 +2307,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>151600</v>
+        <v>34200</v>
       </c>
       <c r="E62" s="3">
-        <v>66900</v>
+        <v>36900</v>
       </c>
       <c r="F62" s="3">
-        <v>69200</v>
+        <v>41100</v>
       </c>
       <c r="G62" s="3">
-        <v>96800</v>
+        <v>76300</v>
       </c>
       <c r="H62" s="3">
-        <v>139700</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+        <v>157200</v>
+      </c>
+      <c r="I62" s="3">
+        <v>138200</v>
+      </c>
+      <c r="J62" s="3">
+        <v>106800</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2439,25 +2439,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2103900</v>
+        <v>1958900</v>
       </c>
       <c r="E66" s="3">
-        <v>1208700</v>
+        <v>1280500</v>
       </c>
       <c r="F66" s="3">
-        <v>1014600</v>
+        <v>1176400</v>
       </c>
       <c r="G66" s="3">
-        <v>929000</v>
+        <v>1178500</v>
       </c>
       <c r="H66" s="3">
-        <v>1159800</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+        <v>1500100</v>
+      </c>
+      <c r="I66" s="3">
+        <v>1437800</v>
+      </c>
+      <c r="J66" s="3">
+        <v>1535200</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2619,25 +2619,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2001900</v>
+        <v>1859200</v>
       </c>
       <c r="E72" s="3">
-        <v>1862400</v>
+        <v>1969700</v>
       </c>
       <c r="F72" s="3">
-        <v>1596500</v>
+        <v>1850300</v>
       </c>
       <c r="G72" s="3">
-        <v>1423900</v>
+        <v>1813300</v>
       </c>
       <c r="H72" s="3">
-        <v>1470700</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+        <v>1917600</v>
+      </c>
+      <c r="I72" s="3">
+        <v>1821900</v>
+      </c>
+      <c r="J72" s="3">
+        <v>1950700</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2751,25 +2751,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2539500</v>
+        <v>2364700</v>
       </c>
       <c r="E76" s="3">
-        <v>2352400</v>
+        <v>2492400</v>
       </c>
       <c r="F76" s="3">
-        <v>2077400</v>
+        <v>2409400</v>
       </c>
       <c r="G76" s="3">
-        <v>2064400</v>
+        <v>2629000</v>
       </c>
       <c r="H76" s="3">
-        <v>2093900</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+        <v>2740800</v>
+      </c>
+      <c r="I76" s="3">
+        <v>2739500</v>
+      </c>
+      <c r="J76" s="3">
+        <v>2907300</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -2836,11 +2836,11 @@
       <c r="H80" s="2">
         <v>43921</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
+      <c r="I80" s="2">
+        <v>43555</v>
+      </c>
+      <c r="J80" s="2">
+        <v>43190</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
@@ -2855,25 +2855,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>234700</v>
+        <v>218500</v>
       </c>
       <c r="E81" s="3">
-        <v>326200</v>
+        <v>345600</v>
       </c>
       <c r="F81" s="3">
-        <v>262900</v>
+        <v>304900</v>
       </c>
       <c r="G81" s="3">
-        <v>9000</v>
+        <v>11500</v>
       </c>
       <c r="H81" s="3">
-        <v>97800</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+        <v>128000</v>
+      </c>
+      <c r="I81" s="3">
+        <v>23800</v>
+      </c>
+      <c r="J81" s="3">
+        <v>84100</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -2903,25 +2903,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>113700</v>
+        <v>89300</v>
       </c>
       <c r="E83" s="3">
-        <v>91200</v>
+        <v>80300</v>
       </c>
       <c r="F83" s="3">
-        <v>97400</v>
+        <v>93900</v>
       </c>
       <c r="G83" s="3">
-        <v>118800</v>
+        <v>134100</v>
       </c>
       <c r="H83" s="3">
-        <v>136600</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+        <v>159800</v>
+      </c>
+      <c r="I83" s="3">
+        <v>169800</v>
+      </c>
+      <c r="J83" s="3">
+        <v>180600</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3101,25 +3101,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>467400</v>
+        <v>435200</v>
       </c>
       <c r="E89" s="3">
-        <v>316600</v>
+        <v>336300</v>
       </c>
       <c r="F89" s="3">
-        <v>281500</v>
+        <v>326200</v>
       </c>
       <c r="G89" s="3">
-        <v>-45200</v>
+        <v>-57700</v>
       </c>
       <c r="H89" s="3">
-        <v>273700</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+        <v>358100</v>
+      </c>
+      <c r="I89" s="3">
+        <v>134200</v>
+      </c>
+      <c r="J89" s="3">
+        <v>249400</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3149,25 +3149,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-37900</v>
+        <v>-35300</v>
       </c>
       <c r="E91" s="3">
-        <v>-35100</v>
+        <v>-37200</v>
       </c>
       <c r="F91" s="3">
-        <v>-42500</v>
+        <v>-49300</v>
       </c>
       <c r="G91" s="3">
-        <v>-52200</v>
+        <v>-66500</v>
       </c>
       <c r="H91" s="3">
-        <v>-71300</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
+        <v>-93300</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-164600</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-103000</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -3248,25 +3248,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-805900</v>
+        <v>-750400</v>
       </c>
       <c r="E94" s="3">
-        <v>-16700</v>
+        <v>-17700</v>
       </c>
       <c r="F94" s="3">
-        <v>-62400</v>
+        <v>-72400</v>
       </c>
       <c r="G94" s="3">
-        <v>216400</v>
+        <v>275500</v>
       </c>
       <c r="H94" s="3">
-        <v>-109800</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+        <v>-143700</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-199600</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-192300</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3296,19 +3296,19 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-97100</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-62900</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-66800</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-50100</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-66700</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -3428,25 +3428,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>566500</v>
+        <v>527500</v>
       </c>
       <c r="E100" s="3">
-        <v>-109000</v>
+        <v>-115500</v>
       </c>
       <c r="F100" s="3">
-        <v>-255400</v>
+        <v>-296200</v>
       </c>
       <c r="G100" s="3">
-        <v>-223600</v>
+        <v>-284700</v>
       </c>
       <c r="H100" s="3">
-        <v>-77800</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>-101800</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-186500</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-271000</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3461,25 +3461,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>58200</v>
+        <v>54200</v>
       </c>
       <c r="E101" s="3">
         <v>1200</v>
       </c>
       <c r="F101" s="3">
-        <v>21500</v>
+        <v>24900</v>
       </c>
       <c r="G101" s="3">
-        <v>23500</v>
+        <v>29900</v>
       </c>
       <c r="H101" s="3">
-        <v>-11200</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+        <v>-14600</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="J101" s="3">
+        <v>700</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -3494,25 +3494,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>286100</v>
+        <v>266400</v>
       </c>
       <c r="E102" s="3">
-        <v>192100</v>
+        <v>204300</v>
       </c>
       <c r="F102" s="3">
-        <v>-14800</v>
+        <v>-17500</v>
       </c>
       <c r="G102" s="3">
-        <v>-29000</v>
+        <v>-37000</v>
       </c>
       <c r="H102" s="3">
-        <v>74900</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>98000</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-257200</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-213200</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/SGAMY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SGAMY_YR_FIN.xlsx
@@ -656,160 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44286</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43921</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43555</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43190</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2864500</v>
+      </c>
+      <c r="E8" s="3">
         <v>3093400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2931000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2643000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2511300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3406900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2992900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3047500</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1577600</v>
+      </c>
+      <c r="E9" s="3">
         <v>1792700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1742000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1590000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1600100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2138400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1906000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1910700</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1286900</v>
+      </c>
+      <c r="E10" s="3">
         <v>1300700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1189100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1053000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>911200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1268600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1087000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1136800</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,41 +835,45 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>186200</v>
+      </c>
+      <c r="E12" s="3">
         <v>164400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>173400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>172400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>204300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>229700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>209800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>217800</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,75 +904,84 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="E14" s="3">
         <v>119600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>20200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-33800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>107200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-15000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>5700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>25700</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>107600</v>
+      </c>
+      <c r="E15" s="3">
         <v>105900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>96600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>113000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>151300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>178800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>188500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>201000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -967,74 +992,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2543100</v>
+      </c>
+      <c r="E17" s="3">
         <v>2717700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2579100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2379100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2452000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3150000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2874900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2880700</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>321400</v>
+      </c>
+      <c r="E18" s="3">
         <v>375800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>352000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>263900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>59300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>256900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>118000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>166900</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1048,173 +1080,189 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>13100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>54000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>27700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>55600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>38300</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>443800</v>
+      </c>
+      <c r="E21" s="3">
         <v>483700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>451700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>363700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>156600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>408000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>250900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>329600</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E22" s="3">
         <v>5100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>4200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>4400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>4800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6700</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>365900</v>
+      </c>
+      <c r="E23" s="3">
         <v>276600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>354100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>312300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-89000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>251900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>63000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>116900</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E24" s="3">
         <v>57500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-106000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>122000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>38400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>28700</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1245,75 +1293,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>300900</v>
+      </c>
+      <c r="E26" s="3">
         <v>219000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>345500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>304800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>17000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>129800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>24600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>88200</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>300900</v>
+      </c>
+      <c r="E27" s="3">
         <v>218500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>345600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>304900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>11500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>128000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>23800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>84100</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1344,9 +1401,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1377,9 +1437,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1410,9 +1473,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1443,75 +1509,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E32" s="3">
         <v>2000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-13100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-54000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-27700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-55600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-38300</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>300800</v>
+      </c>
+      <c r="E33" s="3">
         <v>218500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>345600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>304900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>11500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>128000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>23800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>84100</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1542,80 +1617,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>300800</v>
+      </c>
+      <c r="E35" s="3">
         <v>218500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>345600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>304900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>11500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>128000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>23800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>84100</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44286</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43921</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43555</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43190</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1629,8 +1713,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1644,305 +1729,333 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1338000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1399700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1350400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1255500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1401200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1477800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1240200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1486700</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>53500</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>6500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>50200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>130900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>232500</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>400700</v>
+      </c>
+      <c r="E43" s="3">
         <v>491000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>516700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>415400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>436200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>417700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>392500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>315700</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>625600</v>
+      </c>
+      <c r="E44" s="3">
         <v>540500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>673000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>556100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>478400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>436900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>451400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>382000</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>231700</v>
+      </c>
+      <c r="E45" s="3">
         <v>126700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>121900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>143000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>175800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>117200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>135600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>147200</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2596000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2611500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2661900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2369900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2498200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2499700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2350500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2611500</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>341800</v>
+      </c>
+      <c r="E47" s="3">
         <v>531900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>430500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>496500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>497600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>765200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>900300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>862200</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>326800</v>
+      </c>
+      <c r="E48" s="3">
         <v>397300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>455000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>497000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>557100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>805300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>758200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>735800</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>609300</v>
+      </c>
+      <c r="E49" s="3">
         <v>610100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>99700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>108600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>135600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>167000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>138000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>221100</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1973,9 +2086,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2006,14 +2122,17 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>238200</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -2033,15 +2152,18 @@
       <c r="J52" s="3">
         <v>0</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
+      <c r="K52" s="3">
+        <v>0</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2072,42 +2194,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4305700</v>
+      </c>
+      <c r="E54" s="3">
         <v>4323800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3773000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3586200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3812000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4258900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4193200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4458400</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2121,8 +2249,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2136,206 +2265,225 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>157300</v>
+      </c>
+      <c r="E57" s="3">
         <v>172500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>229900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>201400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>153700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>165700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>223400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>204500</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E58" s="3">
         <v>148800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>127900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>82300</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>216800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>233300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>243300</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>191400</v>
+      </c>
+      <c r="E59" s="3">
         <v>333200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>316200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>186100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>162400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>194600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>138700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>164200</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>628900</v>
+      </c>
+      <c r="E60" s="3">
         <v>895800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>905200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>716300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>540500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>800600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>790000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>795500</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>979200</v>
+      </c>
+      <c r="E61" s="3">
         <v>921200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>303500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>378900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>513600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>483300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>454200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>575900</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>43100</v>
+      </c>
+      <c r="E62" s="3">
         <v>34200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>36900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>41100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>76300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>157200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>138200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>106800</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2366,9 +2514,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,9 +2550,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2432,42 +2586,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1757500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1958900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1280500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1176400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1178500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1500100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1437800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1535200</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2481,8 +2641,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2513,9 +2674,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2546,9 +2710,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2579,9 +2746,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2612,42 +2782,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2103200</v>
+      </c>
+      <c r="E72" s="3">
         <v>1859200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1969700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1850300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1813300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1917600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1821900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1950700</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2678,9 +2854,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2711,9 +2890,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2744,42 +2926,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2548100</v>
+      </c>
+      <c r="E76" s="3">
         <v>2364700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2492400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2409400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2629000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2740800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2739500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2907300</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2810,80 +2998,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44286</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43921</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43555</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43190</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>300800</v>
+      </c>
+      <c r="E81" s="3">
         <v>218500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>345600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>304900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>11500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>128000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>23800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>84100</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2897,41 +3094,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>87100</v>
+      </c>
+      <c r="E83" s="3">
         <v>89300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>80300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>93900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>134100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>159800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>169800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>180600</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2962,9 +3163,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2995,9 +3199,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3028,9 +3235,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3061,9 +3271,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3094,42 +3307,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>139300</v>
+      </c>
+      <c r="E89" s="3">
         <v>435200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>336300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>326200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-57700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>358100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>134200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>249400</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3143,41 +3362,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-35300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-37200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-49300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-66500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-93300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-164600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-103000</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3208,9 +3431,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3241,42 +3467,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-83800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-750400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-17700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-72400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>275500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-143700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-199600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-192300</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3290,13 +3522,14 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -3322,9 +3555,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3355,9 +3591,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3388,9 +3627,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3421,106 +3663,118 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-186900</v>
+      </c>
+      <c r="E100" s="3">
         <v>527500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-115500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-296200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-284700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-101800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-186500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-271000</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E101" s="3">
         <v>54200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>24900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>29900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-14600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>700</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-142900</v>
+      </c>
+      <c r="E102" s="3">
         <v>266400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>204300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-17500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-37000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>98000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-257200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-213200</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SGAMY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SGAMY_YR_FIN.xlsx
@@ -914,7 +914,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-17800</v>
+        <v>-10800</v>
       </c>
       <c r="E14" s="3">
         <v>119600</v>
@@ -1195,7 +1195,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>365900</v>
+        <v>366000</v>
       </c>
       <c r="E23" s="3">
         <v>276600</v>
@@ -1952,7 +1952,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>341800</v>
+        <v>580000</v>
       </c>
       <c r="E47" s="3">
         <v>531900</v>
@@ -2132,7 +2132,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>238200</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -2596,7 +2596,7 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1757500</v>
+        <v>1757400</v>
       </c>
       <c r="E66" s="3">
         <v>1958900</v>
@@ -3529,7 +3529,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/SGAMY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SGAMY_YR_FIN.xlsx
@@ -3529,25 +3529,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>90400</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>66700</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>77500</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>63900</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>87300</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>84600</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
